--- a/data/trans_bre/P8_2_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P8_2_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,23</t>
+          <t>-1,84; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,07</t>
+          <t>-0,48; 3,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,99</t>
+          <t>0,95; 4,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,44</t>
+          <t>-2,44; 3,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 166,83</t>
+          <t>-54,87; 126,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 373,6</t>
+          <t>-23,56; 340,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 2032,3</t>
+          <t>4,86; 1669,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,18</t>
+          <t>0,56; 5,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,74</t>
+          <t>-2,0; 3,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,9</t>
+          <t>-0,63; 3,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -0,15</t>
+          <t>-5,17; -0,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 245,22</t>
+          <t>9,94; 243,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 95,91</t>
+          <t>-40,09; 108,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 223,46</t>
+          <t>-19,13; 210,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,21; -0,65</t>
+          <t>-90,72; 9,83</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,68</t>
+          <t>-0,17; 4,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,85</t>
+          <t>2,29; 7,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,66</t>
+          <t>-0,77; 4,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 3,61</t>
+          <t>-1,87; 3,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 121,18</t>
+          <t>-3,08; 139,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,77; 172,45</t>
+          <t>30,77; 186,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 107,6</t>
+          <t>-11,86; 116,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 86,32</t>
+          <t>-26,83; 93,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,9</t>
+          <t>2,15; 10,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,87</t>
+          <t>1,98; 10,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 6,42</t>
+          <t>-1,04; 6,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 2,09</t>
+          <t>-57,02; 2,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,16; 131,9</t>
+          <t>17,41; 131,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 111,71</t>
+          <t>15,31; 115,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 65,8</t>
+          <t>-6,82; 72,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,53; 19,34</t>
+          <t>-83,5; 21,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 13,03</t>
+          <t>0,66; 13,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 22,28</t>
+          <t>10,5; 22,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 17,45</t>
+          <t>6,18; 17,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,08</t>
+          <t>-0,4; 8,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 60,96</t>
+          <t>1,97; 60,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,61; 128,94</t>
+          <t>45,04; 131,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,03; 102,82</t>
+          <t>25,63; 100,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 43,32</t>
+          <t>-2,29; 43,0</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,93; 34,09</t>
+          <t>19,43; 33,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,73; 25,46</t>
+          <t>9,85; 25,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 20,49</t>
+          <t>6,8; 20,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 16,71</t>
+          <t>-15,61; 16,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,42; 113,09</t>
+          <t>49,12; 112,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,03; 68,97</t>
+          <t>21,0; 69,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,59; 68,07</t>
+          <t>18,39; 69,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,82; 68,39</t>
+          <t>-55,75; 67,81</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 20,98</t>
+          <t>4,6; 20,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 19,45</t>
+          <t>5,01; 19,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 21,87</t>
+          <t>6,77; 21,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,09; 28,96</t>
+          <t>17,65; 28,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 33,64</t>
+          <t>6,05; 32,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 29,57</t>
+          <t>6,71; 30,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,1; 41,4</t>
+          <t>10,84; 40,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,17; 57,72</t>
+          <t>29,94; 57,49</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,12</t>
+          <t>7,27; 11,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,09</t>
+          <t>8,19; 12,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,14</t>
+          <t>6,48; 10,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 6,48</t>
+          <t>-17,84; 6,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,68; 84,71</t>
+          <t>48,79; 84,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,81; 82,53</t>
+          <t>50,46; 83,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,05; 73,47</t>
+          <t>42,13; 76,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 42,99</t>
+          <t>-46,99; 44,65</t>
         </is>
       </c>
     </row>
